--- a/examples/indigo_aryl_alkyl/N_aryl_N_alkyl_indigo.xlsx
+++ b/examples/indigo_aryl_alkyl/N_aryl_N_alkyl_indigo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\My File\ICReDD\labnotes\indigo MLR\new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pecu6\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B369D0B7-B578-4C6C-94DB-D4B3DD840674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E941E280-4A72-4461-BB9D-94BCB19CADC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{23ABDC5F-98FE-4B89-883D-5F8C04F6B499}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{23ABDC5F-98FE-4B89-883D-5F8C04F6B499}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
@@ -293,13 +293,13 @@
     <t>Ar_I_C=O</t>
   </si>
   <si>
-    <t>AKJ-452</t>
-  </si>
-  <si>
     <t>PGOH-30</t>
   </si>
   <si>
     <t>lor</t>
+  </si>
+  <si>
+    <t>AKJ-1-452</t>
   </si>
 </sst>
 </file>
@@ -363,7 +363,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -379,9 +379,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -419,7 +419,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -525,7 +525,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -667,7 +667,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -676,37 +676,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9742D4DA-338A-4D8D-8B29-E291270EB7B7}">
   <dimension ref="A1:Z23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.453125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.81640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9.28515625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7265625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.26953125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.81640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.81640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.81640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.81640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="9.26953125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.54296875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.54296875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="13.54296875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11.453125" style="1" customWidth="1"/>
     <col min="19" max="19" width="12" style="1" customWidth="1"/>
-    <col min="20" max="20" width="11.42578125" style="1" customWidth="1"/>
-    <col min="21" max="22" width="13.28515625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="12.42578125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.453125" style="1" customWidth="1"/>
+    <col min="21" max="22" width="13.26953125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="12.453125" style="1" customWidth="1"/>
     <col min="24" max="24" width="13" style="1" customWidth="1"/>
-    <col min="25" max="25" width="11.42578125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="12.7109375" style="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="25" max="25" width="11.453125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="12.7265625" style="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -783,7 +783,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -865,7 +865,7 @@
         <v>1859.57</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -947,7 +947,7 @@
         <v>1851.44</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>1857.1</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>1854.42</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>1844.58</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>1851.91</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>1843.97</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>1848.3</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>1846.89</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>1848.72</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>1844.96</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>1850.7</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>1847.75</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>1838.69</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>1842.04</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>1838.28</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>1849.08</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>1854.87</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>1848.8</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2423,18 +2423,18 @@
         <v>1848.71</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="E22" s="1">
         <v>0.43759999999999999</v>
@@ -2505,7 +2505,7 @@
         <v>1843.25</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.35">
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
